--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.745547183872592</v>
+        <v>1.583651417379296</v>
       </c>
       <c r="D2" t="n">
-        <v>9.576537996129025</v>
+        <v>1.556187424370967</v>
       </c>
       <c r="E2" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F2" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.41464222185612</v>
+        <v>3.64237936105162</v>
       </c>
       <c r="D3" t="n">
-        <v>22.37457687819355</v>
+        <v>3.635868742706452</v>
       </c>
       <c r="E3" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F3" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.43790832191698</v>
+        <v>2.508660102311509</v>
       </c>
       <c r="D4" t="n">
-        <v>16.08122261940506</v>
+        <v>2.613198675653322</v>
       </c>
       <c r="E4" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F4" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.461369552151748</v>
+        <v>1.212472552224659</v>
       </c>
       <c r="D5" t="n">
-        <v>7.698980078287763</v>
+        <v>1.251084262721762</v>
       </c>
       <c r="E5" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F5" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.90518973538427</v>
+        <v>2.259593331999944</v>
       </c>
       <c r="D6" t="n">
-        <v>12.58017598308459</v>
+        <v>2.044278597251246</v>
       </c>
       <c r="E6" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F6" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.925151005792488</v>
+        <v>1.612837038441279</v>
       </c>
       <c r="D7" t="n">
-        <v>13.31930094929075</v>
+        <v>2.164386404259748</v>
       </c>
       <c r="E7" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F7" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.917090377222865</v>
+        <v>0.7990271862987156</v>
       </c>
       <c r="D8" t="n">
-        <v>4.686149805543988</v>
+        <v>0.7614993434008981</v>
       </c>
       <c r="E8" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F8" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.09242726010606</v>
+        <v>4.240019429767235</v>
       </c>
       <c r="D9" t="n">
-        <v>25.76713238043984</v>
+        <v>4.187159011821474</v>
       </c>
       <c r="E9" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F9" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.83781370307651</v>
+        <v>5.498644726749934</v>
       </c>
       <c r="D10" t="n">
-        <v>33.40515519349126</v>
+        <v>5.428337718942331</v>
       </c>
       <c r="E10" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F10" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.75500818410925</v>
+        <v>7.110188829917753</v>
       </c>
       <c r="D11" t="n">
-        <v>43.2299226058523</v>
+        <v>7.024862423450999</v>
       </c>
       <c r="E11" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F11" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.0170891095147</v>
+        <v>8.452776980296139</v>
       </c>
       <c r="D12" t="n">
-        <v>51.4939219984393</v>
+        <v>8.367762324746387</v>
       </c>
       <c r="E12" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F12" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>14.99625983050568</v>
+        <v>2.436892222457173</v>
       </c>
       <c r="D13" t="n">
-        <v>15.02462056802363</v>
+        <v>2.44150084230384</v>
       </c>
       <c r="E13" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F13" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.80285606158189</v>
+        <v>6.467964110007058</v>
       </c>
       <c r="D14" t="n">
-        <v>40.25838293789433</v>
+        <v>6.541987227407829</v>
       </c>
       <c r="E14" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F14" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>9.265455029465919</v>
+        <v>1.505636442288212</v>
       </c>
       <c r="D15" t="n">
-        <v>9.636019175994575</v>
+        <v>1.565853116099118</v>
       </c>
       <c r="E15" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F15" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.05458259751628</v>
+        <v>4.558869672096395</v>
       </c>
       <c r="D16" t="n">
-        <v>28.55752400746473</v>
+        <v>4.640597651213019</v>
       </c>
       <c r="E16" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F16" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>49.90985167610193</v>
+        <v>8.110350897366564</v>
       </c>
       <c r="D17" t="n">
-        <v>50.19224107063868</v>
+        <v>8.156239173978786</v>
       </c>
       <c r="E17" t="n">
-        <v>15.26508816030608</v>
+        <v>2.480576826049738</v>
       </c>
       <c r="F17" t="n">
-        <v>15.06637082546474</v>
+        <v>2.448285259138021</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
